--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008415679646344133</v>
       </c>
       <c r="C2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>9811796</v>
+        <v>4805078</v>
       </c>
       <c r="L2" t="n">
-        <v>6192839</v>
+        <v>2963846</v>
       </c>
       <c r="M2" t="n">
-        <v>1641591</v>
+        <v>769208</v>
       </c>
       <c r="N2" t="n">
-        <v>90516</v>
+        <v>37776</v>
       </c>
       <c r="O2" t="n">
-        <v>953666</v>
+        <v>454240</v>
       </c>
       <c r="P2" t="n">
-        <v>368871</v>
+        <v>178750</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999322295188904</v>
+        <v>0.9999266862869263</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9735602140426636</v>
+        <v>0.9522756338119507</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9311398863792419</v>
+        <v>0.8928093910217285</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9231709837913513</v>
+        <v>0.865268349647522</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7691118121147156</v>
+        <v>0.6653984189033508</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9371791481971741</v>
+        <v>0.8920589685440063</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9462597966194153</v>
+        <v>0.9137333631515503</v>
       </c>
       <c r="X2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12625956</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="AG2" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AH2" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AI2" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567450881004333</v>
+        <v>0.9567357897758484</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112150073051453</v>
+        <v>0.9112488627433777</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582985401153564</v>
+        <v>0.8582139611244202</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627530455589294</v>
+        <v>0.6625582575798035</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020664095878601</v>
+        <v>0.9019841551780701</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -792,130 +792,130 @@
         <v>0.002018555837031282</v>
       </c>
       <c r="C3" t="n">
-        <v>395</v>
+        <v>199</v>
       </c>
       <c r="D3" t="n">
-        <v>9811796</v>
+        <v>4805078</v>
       </c>
       <c r="E3" t="n">
-        <v>257032</v>
+        <v>225541</v>
       </c>
       <c r="F3" t="n">
-        <v>3125</v>
+        <v>2683</v>
       </c>
       <c r="G3" t="n">
-        <v>512</v>
+        <v>464</v>
       </c>
       <c r="H3" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I3" t="n">
         <v>22</v>
       </c>
       <c r="J3" t="n">
-        <v>20032388</v>
+        <v>10016159</v>
       </c>
       <c r="K3" t="n">
-        <v>22319697</v>
+        <v>11054650</v>
       </c>
       <c r="L3" t="n">
-        <v>25686554</v>
+        <v>12714408</v>
       </c>
       <c r="M3" t="n">
-        <v>30659416</v>
+        <v>15278014</v>
       </c>
       <c r="N3" t="n">
-        <v>32453958</v>
+        <v>16221540</v>
       </c>
       <c r="O3" t="n">
-        <v>31577516</v>
+        <v>15765663</v>
       </c>
       <c r="P3" t="n">
-        <v>32251706</v>
+        <v>16119442</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9740654230117798</v>
+        <v>0.9544986486434937</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9505990147590637</v>
+        <v>0.9093356728553772</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8810760974884033</v>
+        <v>0.8254969716072083</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5083197951316833</v>
+        <v>0.424144446849823</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9370262622833252</v>
+        <v>0.8924638628959656</v>
       </c>
       <c r="W3" t="n">
-        <v>0.954276978969574</v>
+        <v>0.9248145222663879</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9646677</v>
+        <v>4820894</v>
       </c>
       <c r="Z3" t="n">
-        <v>395630</v>
+        <v>197858</v>
       </c>
       <c r="AA3" t="n">
-        <v>17032</v>
+        <v>8531</v>
       </c>
       <c r="AB3" t="n">
-        <v>13547</v>
+        <v>6780</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20033244</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>22150033</v>
+        <v>11077458</v>
       </c>
       <c r="AG3" t="n">
-        <v>25566849</v>
+        <v>12781334</v>
       </c>
       <c r="AH3" t="n">
-        <v>30532165</v>
+        <v>15265735</v>
       </c>
       <c r="AI3" t="n">
-        <v>32421126</v>
+        <v>16210502</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31541812</v>
+        <v>15770758</v>
       </c>
       <c r="AK3" t="n">
-        <v>32246147</v>
+        <v>16123064</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576732516288757</v>
+        <v>0.9576404094696045</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100743532180786</v>
+        <v>0.9101204872131348</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578290939331055</v>
+        <v>0.8577921390533447</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66222083568573</v>
+        <v>0.6621193885803223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016799926757812</v>
+        <v>0.9016509652137756</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -929,282 +929,282 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>245172</v>
+        <v>222753</v>
       </c>
       <c r="E4" t="n">
-        <v>6192839</v>
+        <v>2963846</v>
       </c>
       <c r="F4" t="n">
-        <v>74386</v>
+        <v>70541</v>
       </c>
       <c r="G4" t="n">
-        <v>1042</v>
+        <v>986</v>
       </c>
       <c r="H4" t="n">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="I4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J4" t="n">
-        <v>856</v>
+        <v>463</v>
       </c>
       <c r="K4" t="n">
-        <v>266467</v>
+        <v>240812</v>
       </c>
       <c r="L4" t="n">
-        <v>457976</v>
+        <v>355839</v>
       </c>
       <c r="M4" t="n">
-        <v>136618</v>
+        <v>119774</v>
       </c>
       <c r="N4" t="n">
-        <v>27173</v>
+        <v>18996</v>
       </c>
       <c r="O4" t="n">
-        <v>63926</v>
+        <v>54964</v>
       </c>
       <c r="P4" t="n">
-        <v>20949</v>
+        <v>16876</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999660849571228</v>
+        <v>0.9999633431434631</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9738127589225769</v>
+        <v>0.9533858299255371</v>
       </c>
       <c r="S4" t="n">
-        <v>0.940768837928772</v>
+        <v>0.9009968042373657</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9016324281692505</v>
+        <v>0.8449148535728455</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6120949983596802</v>
+        <v>0.5180613994598389</v>
       </c>
       <c r="V4" t="n">
-        <v>0.937102735042572</v>
+        <v>0.8922614455223083</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9502514600753784</v>
+        <v>0.9192405343055725</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>407180</v>
+        <v>203532</v>
       </c>
       <c r="Z4" t="n">
-        <v>5928834</v>
+        <v>2966404</v>
       </c>
       <c r="AA4" t="n">
-        <v>165287</v>
+        <v>82724</v>
       </c>
       <c r="AB4" t="n">
-        <v>10949</v>
+        <v>5477</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>436131</v>
+        <v>218004</v>
       </c>
       <c r="AG4" t="n">
-        <v>577681</v>
+        <v>288913</v>
       </c>
       <c r="AH4" t="n">
-        <v>263869</v>
+        <v>132053</v>
       </c>
       <c r="AI4" t="n">
-        <v>60005</v>
+        <v>30034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99630</v>
+        <v>49869</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572089314460754</v>
+        <v>0.9571878910064697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106443524360657</v>
+        <v>0.9106842875480652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580637574195862</v>
+        <v>0.8580030798912048</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624868512153625</v>
+        <v>0.6623387336730957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018731117248535</v>
+        <v>0.9018175005912781</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>343</v>
+        <v>176</v>
       </c>
       <c r="D5" t="n">
-        <v>13141</v>
+        <v>10851</v>
       </c>
       <c r="E5" t="n">
-        <v>167015</v>
+        <v>113247</v>
       </c>
       <c r="F5" t="n">
-        <v>1641591</v>
+        <v>769208</v>
       </c>
       <c r="G5" t="n">
-        <v>11293</v>
+        <v>8631</v>
       </c>
       <c r="H5" t="n">
-        <v>28941</v>
+        <v>28865</v>
       </c>
       <c r="I5" t="n">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>261240</v>
+        <v>229060</v>
       </c>
       <c r="L5" t="n">
-        <v>321831</v>
+        <v>295507</v>
       </c>
       <c r="M5" t="n">
-        <v>221575</v>
+        <v>162604</v>
       </c>
       <c r="N5" t="n">
-        <v>87553</v>
+        <v>51288</v>
       </c>
       <c r="O5" t="n">
-        <v>64092</v>
+        <v>54733</v>
       </c>
       <c r="P5" t="n">
-        <v>17674</v>
+        <v>14532</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999737739562988</v>
+        <v>0.9999716281890869</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9838420152664185</v>
+        <v>0.9712257385253906</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9761229157447815</v>
+        <v>0.9601125717163086</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9890323877334595</v>
+        <v>0.9827076196670532</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9964872002601624</v>
+        <v>0.9956958889961243</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9960801601409912</v>
+        <v>0.9932823181152344</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9988173842430115</v>
+        <v>0.9980766177177429</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15974</v>
+        <v>7983</v>
       </c>
       <c r="Z5" t="n">
-        <v>169599</v>
+        <v>84824</v>
       </c>
       <c r="AA5" t="n">
-        <v>1598278</v>
+        <v>799301</v>
       </c>
       <c r="AB5" t="n">
-        <v>19854</v>
+        <v>9943</v>
       </c>
       <c r="AC5" t="n">
-        <v>58195</v>
+        <v>29128</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>426359</v>
+        <v>213244</v>
       </c>
       <c r="AG5" t="n">
-        <v>585836</v>
+        <v>292949</v>
       </c>
       <c r="AH5" t="n">
-        <v>264888</v>
+        <v>132511</v>
       </c>
       <c r="AI5" t="n">
-        <v>60148</v>
+        <v>30093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100066</v>
+        <v>50057</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735912084579468</v>
+        <v>0.9735910296440125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643740057945251</v>
+        <v>0.9643676280975342</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838098883628845</v>
+        <v>0.9837985038757324</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210225105286</v>
+        <v>0.9963179230690002</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938854575157166</v>
+        <v>0.9938806891441345</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983761310577393</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D6" t="n">
-        <v>8074</v>
+        <v>7146</v>
       </c>
       <c r="E6" t="n">
-        <v>32932</v>
+        <v>16082</v>
       </c>
       <c r="F6" t="n">
-        <v>28915</v>
+        <v>16501</v>
       </c>
       <c r="G6" t="n">
-        <v>90516</v>
+        <v>37776</v>
       </c>
       <c r="H6" t="n">
-        <v>16914</v>
+        <v>10987</v>
       </c>
       <c r="I6" t="n">
-        <v>635</v>
+        <v>507</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12866</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>10669</v>
+        <v>5341</v>
       </c>
       <c r="AA6" t="n">
-        <v>21709</v>
+        <v>10859</v>
       </c>
       <c r="AB6" t="n">
-        <v>117921</v>
+        <v>58971</v>
       </c>
       <c r="AC6" t="n">
-        <v>13942</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E7" t="n">
-        <v>899</v>
+        <v>879</v>
       </c>
       <c r="F7" t="n">
-        <v>29830</v>
+        <v>29702</v>
       </c>
       <c r="G7" t="n">
-        <v>13929</v>
+        <v>8660</v>
       </c>
       <c r="H7" t="n">
-        <v>953666</v>
+        <v>454240</v>
       </c>
       <c r="I7" t="n">
-        <v>19384</v>
+        <v>15448</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1621</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>59181</v>
+        <v>29609</v>
       </c>
       <c r="AB7" t="n">
-        <v>15125</v>
+        <v>7569</v>
       </c>
       <c r="AC7" t="n">
-        <v>917692</v>
+        <v>458916</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="G8" t="n">
-        <v>397</v>
+        <v>255</v>
       </c>
       <c r="H8" t="n">
-        <v>16753</v>
+        <v>13800</v>
       </c>
       <c r="I8" t="n">
-        <v>368871</v>
+        <v>178750</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
